--- a/data/raw/Copa_2026_2027/boxscores/FCBQ_PBP_CANXAM&PA_-_AECAM_vs_RAMON_SOLER_CB_SALT_73-59_analysis.xlsx
+++ b/data/raw/Copa_2026_2027/boxscores/FCBQ_PBP_CANXAM&PA_-_AECAM_vs_RAMON_SOLER_CB_SALT_73-59_analysis.xlsx
@@ -564,19 +564,19 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>92.98</v>
+        <v>93.48</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>78.51000000000001</v>
+        <v>80.23</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>63.45</v>
+        <v>63.12</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>41.18</v>
+        <v>42.03</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>31.07</v>
+        <v>30.8</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>50</v>
@@ -643,13 +643,13 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>92.98</v>
+        <v>93.48</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>63.45</v>
+        <v>63.12</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>78.51000000000001</v>
+        <v>80.23</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>30.88</v>
@@ -1089,7 +1089,7 @@
         <v>0</v>
       </c>
       <c r="AS8" s="2" t="n">
-        <v>13.13</v>
+        <v>13.02</v>
       </c>
     </row>
     <row r="9">
@@ -1367,7 +1367,7 @@
         <v>0</v>
       </c>
       <c r="AS10" s="2" t="n">
-        <v>20.02</v>
+        <v>19.85</v>
       </c>
     </row>
     <row r="11">
@@ -1508,7 +1508,7 @@
         <v>1.67</v>
       </c>
       <c r="AS11" s="2" t="n">
-        <v>11.77</v>
+        <v>11.67</v>
       </c>
     </row>
     <row r="12">
@@ -1649,7 +1649,7 @@
         <v>0.4</v>
       </c>
       <c r="AS12" s="2" t="n">
-        <v>26.24</v>
+        <v>26.02</v>
       </c>
     </row>
     <row r="13">
@@ -1790,7 +1790,7 @@
         <v>0.29</v>
       </c>
       <c r="AS13" s="2" t="n">
-        <v>24.65</v>
+        <v>24.44</v>
       </c>
     </row>
     <row r="14">
@@ -1931,7 +1931,7 @@
         <v>0.33</v>
       </c>
       <c r="AS14" s="2" t="n">
-        <v>16.47</v>
+        <v>16.33</v>
       </c>
     </row>
     <row r="15">
@@ -1941,13 +1941,13 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>3</v>
@@ -1995,7 +1995,7 @@
         <v>0</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U15" s="3" t="n">
         <v>0</v>
@@ -2054,25 +2054,25 @@
         </is>
       </c>
       <c r="AM15" s="2" t="n">
-        <v>10.88</v>
+        <v>11.88</v>
       </c>
       <c r="AN15" s="2" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="AO15" s="2" t="n">
-        <v>45.96</v>
+        <v>50.51</v>
       </c>
       <c r="AP15" s="2" t="n">
-        <v>0.92</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AR15" s="2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AS15" s="2" t="n">
-        <v>13.2</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="16">
@@ -2213,7 +2213,7 @@
         <v>0</v>
       </c>
       <c r="AS16" s="2" t="n">
-        <v>8.25</v>
+        <v>8.18</v>
       </c>
     </row>
     <row r="17">
@@ -2354,7 +2354,7 @@
         <v>0</v>
       </c>
       <c r="AS17" s="2" t="n">
-        <v>14.73</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="18">
@@ -2495,7 +2495,7 @@
         <v>0</v>
       </c>
       <c r="AS18" s="2" t="n">
-        <v>8.24</v>
+        <v>8.17</v>
       </c>
     </row>
     <row r="19">
@@ -2642,13 +2642,13 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>8</v>
@@ -2696,7 +2696,7 @@
         <v>0</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U20" s="3" t="n">
         <v>3</v>
@@ -2755,19 +2755,19 @@
         </is>
       </c>
       <c r="AM20" s="2" t="n">
-        <v>79.88</v>
+        <v>80.88</v>
       </c>
       <c r="AN20" s="2" t="n">
-        <v>41.18</v>
+        <v>42.03</v>
       </c>
       <c r="AO20" s="2" t="n">
-        <v>45.69</v>
+        <v>46.36</v>
       </c>
       <c r="AP20" s="2" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="AQ20" s="2" t="n">
-        <v>31.07</v>
+        <v>30.8</v>
       </c>
       <c r="AR20" s="2" t="n">
         <v>0.25</v>
